--- a/e2e_t1.xlsx
+++ b/e2e_t1.xlsx
@@ -28,7 +28,7 @@
     <t>E2E검증_방식1</t>
   </si>
   <si>
-    <t>재무모델 (Financial Model) — 재생E AI Agent 자동생성  ·  2026-09-15</t>
+    <t>재무모델 (Financial Model) — 재생E AI Agent 자동생성  ·  2026-09-21</t>
   </si>
   <si>
     <t>No</t>

--- a/e2e_t1.xlsx
+++ b/e2e_t1.xlsx
@@ -28,7 +28,7 @@
     <t>E2E검증_방식1</t>
   </si>
   <si>
-    <t>재무모델 (Financial Model) — 재생E AI Agent 자동생성  ·  2026-09-21</t>
+    <t>재무모델 (Financial Model) — 재생E AI Agent 자동생성  ·  2026-09-22</t>
   </si>
   <si>
     <t>No</t>

--- a/e2e_t1.xlsx
+++ b/e2e_t1.xlsx
@@ -28,7 +28,7 @@
     <t>E2E검증_방식1</t>
   </si>
   <si>
-    <t>재무모델 (Financial Model) — 재생E AI Agent 자동생성  ·  2026-09-22</t>
+    <t>재무모델 (Financial Model) — 재생E AI Agent 자동생성  ·  2026-09-23</t>
   </si>
   <si>
     <t>No</t>

--- a/e2e_t1.xlsx
+++ b/e2e_t1.xlsx
@@ -28,7 +28,7 @@
     <t>E2E검증_방식1</t>
   </si>
   <si>
-    <t>재무모델 (Financial Model) — 재생E AI Agent 자동생성  ·  2026-09-23</t>
+    <t>재무모델 (Financial Model) — 재생E AI Agent 자동생성  ·  2026-10-02</t>
   </si>
   <si>
     <t>No</t>
